--- a/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/FIX NAC.xlsx
+++ b/LISTAS_ORDENADAS/MI/Tornillos Pitones Arandelas Tuercas/FIX NAC.xlsx
@@ -780,14 +780,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="n">
-        <v>45216.53877371446</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="14">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -809,8 +805,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="14">
       <c r="A11" s="15" t="inlineStr">
         <is>
@@ -818,16 +812,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
     <row r="22" ht="24.75" customHeight="1" s="14">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -835,7 +819,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="18" customHeight="1" s="14">
       <c r="A24" s="8" t="inlineStr">
         <is>
@@ -868,7 +851,7 @@
       </c>
       <c r="C25" s="23" t="n"/>
       <c r="D25" s="6" t="n">
-        <v>2828.504</v>
+        <v>2337.606</v>
       </c>
       <c r="E25" s="3" t="n"/>
     </row>
@@ -885,7 +868,7 @@
       </c>
       <c r="C26" s="23" t="n"/>
       <c r="D26" s="7" t="n">
-        <v>3486.045</v>
+        <v>2881.029</v>
       </c>
       <c r="E26" s="3" t="n"/>
     </row>
@@ -902,7 +885,7 @@
       </c>
       <c r="C27" s="23" t="n"/>
       <c r="D27" s="6" t="n">
-        <v>3814.828</v>
+        <v>3152.75</v>
       </c>
       <c r="E27" s="3" t="n"/>
     </row>
@@ -919,7 +902,7 @@
       </c>
       <c r="C28" s="23" t="n"/>
       <c r="D28" s="6" t="n">
-        <v>4658.527</v>
+        <v>3850.023</v>
       </c>
     </row>
     <row r="29" s="14"/>
@@ -962,7 +945,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="6" t="n">
-        <v>3191.115</v>
+        <v>2637.285</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="14">
@@ -978,7 +961,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="6" t="n">
-        <v>3831.776</v>
+        <v>3166.757</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="14">
@@ -994,7 +977,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="6" t="n">
-        <v>4370.87</v>
+        <v>3612.289</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="14">
@@ -1010,7 +993,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="6" t="n">
-        <v>5052.585</v>
+        <v>4175.69</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="14">
@@ -1026,7 +1009,7 @@
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="6" t="n">
-        <v>5980.911</v>
+        <v>4942.902</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="14">
@@ -1042,7 +1025,7 @@
       </c>
       <c r="C38" s="23" t="n"/>
       <c r="D38" s="6" t="n">
-        <v>6947.943</v>
+        <v>5742.102</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="14">
@@ -1058,7 +1041,7 @@
       </c>
       <c r="C39" s="23" t="n"/>
       <c r="D39" s="6" t="n">
-        <v>8026.152</v>
+        <v>6633.184</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="14">
@@ -1074,7 +1057,7 @@
       </c>
       <c r="C40" s="23" t="n"/>
       <c r="D40" s="6" t="n">
-        <v>9597.558999999999</v>
+        <v>7931.867</v>
       </c>
     </row>
     <row r="41" s="14"/>
@@ -1117,7 +1100,7 @@
       </c>
       <c r="C45" s="23" t="n"/>
       <c r="D45" s="6" t="n">
-        <v>3964.707</v>
+        <v>3276.617</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="14">
@@ -1133,7 +1116,7 @@
       </c>
       <c r="C46" s="23" t="n"/>
       <c r="D46" s="6" t="n">
-        <v>4689.963</v>
+        <v>3876.003</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="14">
@@ -1149,7 +1132,7 @@
       </c>
       <c r="C47" s="23" t="n"/>
       <c r="D47" s="6" t="n">
-        <v>5659.389</v>
+        <v>4677.181</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="14">
@@ -1165,7 +1148,7 @@
       </c>
       <c r="C48" s="23" t="n"/>
       <c r="D48" s="6" t="n">
-        <v>6229.912</v>
+        <v>5148.687</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="14">
@@ -1181,7 +1164,7 @@
       </c>
       <c r="C49" s="23" t="n"/>
       <c r="D49" s="6" t="n">
-        <v>7675.579</v>
+        <v>6343.454</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="14">
@@ -1197,7 +1180,7 @@
       </c>
       <c r="C50" s="23" t="n"/>
       <c r="D50" s="6" t="n">
-        <v>8521.73</v>
+        <v>7042.752</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="14">
@@ -1213,7 +1196,7 @@
       </c>
       <c r="C51" s="23" t="n"/>
       <c r="D51" s="6" t="n">
-        <v>9346.102000000001</v>
+        <v>7724.051</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="14">
@@ -1229,7 +1212,7 @@
       </c>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="6" t="n">
-        <v>10661.209</v>
+        <v>8810.915999999999</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="14">
@@ -1245,10 +1228,9 @@
       </c>
       <c r="C53" s="23" t="n"/>
       <c r="D53" s="6" t="n">
-        <v>12015.036</v>
-      </c>
-    </row>
-    <row r="54"/>
+        <v>9929.781999999999</v>
+      </c>
+    </row>
     <row r="55" ht="24.75" customHeight="1" s="14">
       <c r="A55" s="16" t="inlineStr">
         <is>
@@ -1256,7 +1238,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57" ht="18" customHeight="1" s="14">
       <c r="A57" s="8" t="inlineStr">
         <is>
@@ -1288,7 +1269,7 @@
       </c>
       <c r="C58" s="23" t="n"/>
       <c r="D58" s="6" t="n">
-        <v>5345.122</v>
+        <v>4417.456</v>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="14">
@@ -1304,7 +1285,7 @@
       </c>
       <c r="C59" s="23" t="n"/>
       <c r="D59" s="6" t="n">
-        <v>6229.912</v>
+        <v>5148.687</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="14">
@@ -1320,7 +1301,7 @@
       </c>
       <c r="C60" s="23" t="n"/>
       <c r="D60" s="6" t="n">
-        <v>6986.591</v>
+        <v>5774.042</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="14">
@@ -1336,7 +1317,7 @@
       </c>
       <c r="C61" s="23" t="n"/>
       <c r="D61" s="6" t="n">
-        <v>8219.519</v>
+        <v>6792.991</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="14">
@@ -1352,7 +1333,7 @@
       </c>
       <c r="C62" s="23" t="n"/>
       <c r="D62" s="6" t="n">
-        <v>9476.642</v>
+        <v>7831.935</v>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="14">
@@ -1368,7 +1349,7 @@
       </c>
       <c r="C63" s="23" t="n"/>
       <c r="D63" s="6" t="n">
-        <v>11011.754</v>
+        <v>9100.623</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1" s="14">
@@ -1384,7 +1365,7 @@
       </c>
       <c r="C64" s="23" t="n"/>
       <c r="D64" s="6" t="n">
-        <v>12305.126</v>
+        <v>10169.525</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="14">
@@ -1400,7 +1381,7 @@
       </c>
       <c r="C65" s="23" t="n"/>
       <c r="D65" s="6" t="n">
-        <v>13127.07</v>
+        <v>10848.818</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="14">
@@ -1416,7 +1397,7 @@
       </c>
       <c r="C66" s="23" t="n"/>
       <c r="D66" s="6" t="n">
-        <v>14916.046</v>
+        <v>12327.311</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="14">
@@ -1432,7 +1413,7 @@
       </c>
       <c r="C67" s="23" t="n"/>
       <c r="D67" s="6" t="n">
-        <v>16076.475</v>
+        <v>13286.343</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="14">
@@ -1448,7 +1429,7 @@
       </c>
       <c r="C68" s="23" t="n"/>
       <c r="D68" s="6" t="n">
-        <v>17261</v>
+        <v>14265.289</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="14">
@@ -1464,10 +1445,9 @@
       </c>
       <c r="C69" s="23" t="n"/>
       <c r="D69" s="6" t="n">
-        <v>19557.651</v>
-      </c>
-    </row>
-    <row r="70"/>
+        <v>16163.348</v>
+      </c>
+    </row>
     <row r="71" ht="24.75" customHeight="1" s="14">
       <c r="A71" s="16" t="inlineStr">
         <is>
@@ -1475,7 +1455,6 @@
         </is>
       </c>
     </row>
-    <row r="72"/>
     <row r="73" ht="18" customHeight="1" s="14">
       <c r="A73" s="8" t="inlineStr">
         <is>
@@ -1507,7 +1486,7 @@
       </c>
       <c r="C74" s="23" t="n"/>
       <c r="D74" s="6" t="n">
-        <v>7929.431</v>
+        <v>6553.249</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="14">
@@ -1523,7 +1502,7 @@
       </c>
       <c r="C75" s="23" t="n"/>
       <c r="D75" s="6" t="n">
-        <v>8872.273999999999</v>
+        <v>7332.458</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="14">
@@ -1539,7 +1518,7 @@
       </c>
       <c r="C76" s="23" t="n"/>
       <c r="D76" s="6" t="n">
-        <v>9802.257</v>
+        <v>8101.039</v>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="14">
@@ -1555,7 +1534,7 @@
       </c>
       <c r="C77" s="23" t="n"/>
       <c r="D77" s="6" t="n">
-        <v>12957.882</v>
+        <v>10708.994</v>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="14">
@@ -1571,7 +1550,7 @@
       </c>
       <c r="C78" s="23" t="n"/>
       <c r="D78" s="6" t="n">
-        <v>14746.813</v>
+        <v>12187.449</v>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="14">
@@ -1587,7 +1566,7 @@
       </c>
       <c r="C79" s="23" t="n"/>
       <c r="D79" s="6" t="n">
-        <v>16035.346</v>
+        <v>13252.352</v>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="14">
@@ -1603,7 +1582,7 @@
       </c>
       <c r="C80" s="23" t="n"/>
       <c r="D80" s="6" t="n">
-        <v>17551.117</v>
+        <v>14505.055</v>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="14">
@@ -1619,7 +1598,7 @@
       </c>
       <c r="C81" s="23" t="n"/>
       <c r="D81" s="6" t="n">
-        <v>19151.505</v>
+        <v>15827.69</v>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1" s="14">
@@ -1635,7 +1614,7 @@
       </c>
       <c r="C82" s="23" t="n"/>
       <c r="D82" s="6" t="n">
-        <v>20887.287</v>
+        <v>17262.221</v>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="14">
@@ -1651,7 +1630,7 @@
       </c>
       <c r="C83" s="23" t="n"/>
       <c r="D83" s="6" t="n">
-        <v>22734.286</v>
+        <v>18788.666</v>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1" s="14">
@@ -1667,7 +1646,7 @@
       </c>
       <c r="C84" s="23" t="n"/>
       <c r="D84" s="6" t="n">
-        <v>26326.692</v>
+        <v>21757.596</v>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1" s="14">
@@ -1683,10 +1662,9 @@
       </c>
       <c r="C85" s="23" t="n"/>
       <c r="D85" s="6" t="n">
-        <v>29948.078</v>
-      </c>
-    </row>
-    <row r="86"/>
+        <v>24750.477</v>
+      </c>
+    </row>
     <row r="87" ht="24.75" customHeight="1" s="14">
       <c r="A87" s="16" t="inlineStr">
         <is>
@@ -1694,7 +1672,6 @@
         </is>
       </c>
     </row>
-    <row r="88"/>
     <row r="89" ht="18" customHeight="1" s="14">
       <c r="A89" s="8" t="inlineStr">
         <is>
@@ -1726,7 +1703,7 @@
       </c>
       <c r="C90" s="23" t="n"/>
       <c r="D90" s="6" t="n">
-        <v>9742.558000000001</v>
+        <v>8051.701</v>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="14">
@@ -1742,7 +1719,7 @@
       </c>
       <c r="C91" s="23" t="n"/>
       <c r="D91" s="6" t="n">
-        <v>10915.047</v>
+        <v>9020.700000000001</v>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="14">
@@ -1758,7 +1735,7 @@
       </c>
       <c r="C92" s="23" t="n"/>
       <c r="D92" s="6" t="n">
-        <v>13489.702</v>
+        <v>11148.514</v>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="14">
@@ -1774,7 +1751,7 @@
       </c>
       <c r="C93" s="23" t="n"/>
       <c r="D93" s="6" t="n">
-        <v>15375.373</v>
+        <v>12706.92</v>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="14">
@@ -1790,7 +1767,7 @@
       </c>
       <c r="C94" s="23" t="n"/>
       <c r="D94" s="6" t="n">
-        <v>17261</v>
+        <v>14265.289</v>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="14">
@@ -1806,7 +1783,7 @@
       </c>
       <c r="C95" s="23" t="n"/>
       <c r="D95" s="6" t="n">
-        <v>19195.036</v>
+        <v>15863.666</v>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="14">
@@ -1822,7 +1799,7 @@
       </c>
       <c r="C96" s="23" t="n"/>
       <c r="D96" s="6" t="n">
-        <v>21104.855</v>
+        <v>17442.029</v>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="14">
@@ -1838,7 +1815,7 @@
       </c>
       <c r="C97" s="23" t="n"/>
       <c r="D97" s="6" t="n">
-        <v>23280.595</v>
+        <v>19240.161</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1" s="14">
@@ -1854,7 +1831,7 @@
       </c>
       <c r="C98" s="23" t="n"/>
       <c r="D98" s="6" t="n">
-        <v>25698.12</v>
+        <v>21238.115</v>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1" s="14">
@@ -1870,7 +1847,7 @@
       </c>
       <c r="C99" s="23" t="n"/>
       <c r="D99" s="6" t="n">
-        <v>27559.602</v>
+        <v>22776.531</v>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="14">
@@ -1886,7 +1863,7 @@
       </c>
       <c r="C100" s="23" t="n"/>
       <c r="D100" s="6" t="n">
-        <v>31693.563</v>
+        <v>26193.027</v>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1" s="14">
@@ -1902,7 +1879,7 @@
       </c>
       <c r="C101" s="23" t="n"/>
       <c r="D101" s="6" t="n">
-        <v>35851.665</v>
+        <v>29629.475</v>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="14">
@@ -1918,7 +1895,7 @@
       </c>
       <c r="C102" s="23" t="n"/>
       <c r="D102" s="6" t="n">
-        <v>40033.954</v>
+        <v>33085.913</v>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="14">
@@ -1934,10 +1911,9 @@
       </c>
       <c r="C103" s="23" t="n"/>
       <c r="D103" s="6" t="n">
-        <v>44216.23</v>
-      </c>
-    </row>
-    <row r="104"/>
+        <v>36542.339</v>
+      </c>
+    </row>
     <row r="105" ht="24.75" customHeight="1" s="14">
       <c r="A105" s="16" t="inlineStr">
         <is>
@@ -1945,7 +1921,6 @@
         </is>
       </c>
     </row>
-    <row r="106"/>
     <row r="107" ht="18" customHeight="1" s="14">
       <c r="A107" s="8" t="inlineStr">
         <is>
@@ -1977,7 +1952,7 @@
       </c>
       <c r="C108" s="23" t="n"/>
       <c r="D108" s="6" t="n">
-        <v>23643.244</v>
+        <v>19539.871</v>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="14">
@@ -1993,7 +1968,7 @@
       </c>
       <c r="C109" s="23" t="n"/>
       <c r="D109" s="6" t="n">
-        <v>26520.105</v>
+        <v>21917.442</v>
       </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="14">
@@ -2009,7 +1984,7 @@
       </c>
       <c r="C110" s="23" t="n"/>
       <c r="D110" s="6" t="n">
-        <v>29348.554</v>
+        <v>24255.004</v>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1" s="14">
@@ -2025,7 +2000,7 @@
       </c>
       <c r="C111" s="23" t="n"/>
       <c r="D111" s="6" t="n">
-        <v>32394.601</v>
+        <v>26772.397</v>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1" s="14">
@@ -2041,7 +2016,7 @@
       </c>
       <c r="C112" s="23" t="n"/>
       <c r="D112" s="6" t="n">
-        <v>35375.435</v>
+        <v>29235.896</v>
       </c>
     </row>
     <row r="113" ht="18" customHeight="1" s="14">
@@ -2057,7 +2032,7 @@
       </c>
       <c r="C113" s="23" t="n"/>
       <c r="D113" s="6" t="n">
-        <v>41363.579</v>
+        <v>34184.776</v>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1" s="14">
@@ -2073,7 +2048,7 @@
       </c>
       <c r="C114" s="23" t="n"/>
       <c r="D114" s="6" t="n">
-        <v>47383.199</v>
+        <v>39159.668</v>
       </c>
     </row>
     <row r="115" ht="18" customHeight="1" s="14">
@@ -2089,7 +2064,7 @@
       </c>
       <c r="C115" s="23" t="n"/>
       <c r="D115" s="6" t="n">
-        <v>53426.965</v>
+        <v>44154.516</v>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="14">
@@ -2105,7 +2080,7 @@
       </c>
       <c r="C116" s="23" t="n"/>
       <c r="D116" s="6" t="n">
-        <v>59736.666</v>
+        <v>49369.145</v>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="14">
@@ -2121,7 +2096,7 @@
       </c>
       <c r="C117" s="23" t="n"/>
       <c r="D117" s="6" t="n">
-        <v>66312.268</v>
+        <v>54803.527</v>
       </c>
     </row>
     <row r="118" ht="18" customHeight="1" s="14">
@@ -2137,7 +2112,7 @@
       </c>
       <c r="C118" s="23" t="n"/>
       <c r="D118" s="6" t="n">
-        <v>79777.81200000001</v>
+        <v>65932.076</v>
       </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="14">
@@ -2153,7 +2128,7 @@
       </c>
       <c r="C119" s="23" t="n"/>
       <c r="D119" s="6" t="n">
-        <v>87272.099</v>
+        <v>72125.702</v>
       </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="14">
@@ -2169,7 +2144,7 @@
       </c>
       <c r="C120" s="23" t="n"/>
       <c r="D120" s="6" t="n">
-        <v>94766.374</v>
+        <v>78319.317</v>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1" s="14">
@@ -2185,7 +2160,7 @@
       </c>
       <c r="C121" s="23" t="n"/>
       <c r="D121" s="6" t="n">
-        <v>102502.396</v>
+        <v>84712.724</v>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1" s="14">
@@ -2201,11 +2176,9 @@
       </c>
       <c r="C122" s="23" t="n"/>
       <c r="D122" s="6" t="n">
-        <v>119642.541</v>
-      </c>
-    </row>
-    <row r="123"/>
-    <row r="124"/>
+        <v>98878.133</v>
+      </c>
+    </row>
     <row r="125" ht="15" customHeight="1" s="14">
       <c r="A125" s="21" t="inlineStr">
         <is>
@@ -2224,96 +2197,96 @@
     </row>
   </sheetData>
   <mergeCells count="90">
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B53:C53"/>
     <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B81:C81"/>
     <mergeCell ref="B121:C121"/>
     <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B68:C68"/>
     <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B111:C111"/>
-    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="A87:C87"/>
     <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B94:C94"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="B24:C24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
